--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$5</f>
+              <f>'OssDsign'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$5</f>
+              <f>'OssDsign'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$5</f>
+              <f>'OssDsign'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$5</f>
+              <f>'OssDsign'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$5</f>
+              <f>'Smart Eye'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$5</f>
+              <f>'Smart Eye'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$5</f>
+              <f>'Smart Eye'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$5</f>
+              <f>'Smart Eye'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$5</f>
+              <f>'Integrum'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$5</f>
+              <f>'Integrum'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$5</f>
+              <f>'Integrum'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$5</f>
+              <f>'Integrum'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1081,23 @@
       </c>
       <c r="D5" s="2">
         <f>B5+C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2937</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6+C6</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1192,6 +1209,23 @@
       </c>
       <c r="D5" s="2">
         <f>B5+C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11709</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>7043</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6+C6</f>
         <v/>
       </c>
     </row>
@@ -1207,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1306,6 +1340,23 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6+C6</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$6</f>
+              <f>'OssDsign'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$6</f>
+              <f>'OssDsign'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$6</f>
+              <f>'OssDsign'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$6</f>
+              <f>'OssDsign'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$6</f>
+              <f>'Smart Eye'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$6</f>
+              <f>'Smart Eye'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$6</f>
+              <f>'Smart Eye'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$6</f>
+              <f>'Smart Eye'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$6</f>
+              <f>'Integrum'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$6</f>
+              <f>'Integrum'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$6</f>
+              <f>'Integrum'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$6</f>
+              <f>'Integrum'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1098,6 +1098,23 @@
       </c>
       <c r="D6" s="2">
         <f>B6+C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2937</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7+C7</f>
         <v/>
       </c>
     </row>
@@ -1113,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1226,6 +1243,23 @@
       </c>
       <c r="D6" s="2">
         <f>B6+C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>11709</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>7046</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7+C7</f>
         <v/>
       </c>
     </row>
@@ -1241,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1357,6 +1391,23 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7+C7</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$7</f>
+              <f>'OssDsign'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$7</f>
+              <f>'OssDsign'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$7</f>
+              <f>'OssDsign'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$7</f>
+              <f>'OssDsign'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$7</f>
+              <f>'Smart Eye'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$7</f>
+              <f>'Smart Eye'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$7</f>
+              <f>'Smart Eye'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$7</f>
+              <f>'Smart Eye'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$7</f>
+              <f>'Integrum'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$7</f>
+              <f>'Integrum'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$7</f>
+              <f>'Integrum'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$7</f>
+              <f>'Integrum'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1115,6 +1115,23 @@
       </c>
       <c r="D7" s="2">
         <f>B7+C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D8" s="2">
+        <f>B8+C8</f>
         <v/>
       </c>
     </row>
@@ -1130,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1260,6 +1277,23 @@
       </c>
       <c r="D7" s="2">
         <f>B7+C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11711</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7052</v>
+      </c>
+      <c r="D8" s="2">
+        <f>B8+C8</f>
         <v/>
       </c>
     </row>
@@ -1275,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1408,6 +1442,23 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="D8" s="2">
+        <f>B8+C8</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$8</f>
+              <f>'OssDsign'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$8</f>
+              <f>'OssDsign'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$8</f>
+              <f>'OssDsign'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$8</f>
+              <f>'OssDsign'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$8</f>
+              <f>'Smart Eye'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$8</f>
+              <f>'Smart Eye'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$8</f>
+              <f>'Smart Eye'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$8</f>
+              <f>'Smart Eye'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$8</f>
+              <f>'Integrum'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$8</f>
+              <f>'Integrum'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$8</f>
+              <f>'Integrum'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$8</f>
+              <f>'Integrum'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1132,6 +1132,23 @@
       </c>
       <c r="D8" s="2">
         <f>B8+C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D9" s="2">
+        <f>B9+C9</f>
         <v/>
       </c>
     </row>
@@ -1147,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1294,6 +1311,23 @@
       </c>
       <c r="D8" s="2">
         <f>B8+C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>11637</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7063</v>
+      </c>
+      <c r="D9" s="2">
+        <f>B9+C9</f>
         <v/>
       </c>
     </row>
@@ -1309,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1459,6 +1493,23 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D9" s="2">
+        <f>B9+C9</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$9</f>
+              <f>'OssDsign'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$9</f>
+              <f>'OssDsign'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$9</f>
+              <f>'OssDsign'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$9</f>
+              <f>'OssDsign'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$9</f>
+              <f>'Smart Eye'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$9</f>
+              <f>'Smart Eye'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$9</f>
+              <f>'Smart Eye'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$9</f>
+              <f>'Smart Eye'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$9</f>
+              <f>'Integrum'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$9</f>
+              <f>'Integrum'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$9</f>
+              <f>'Integrum'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$9</f>
+              <f>'Integrum'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,23 @@
       </c>
       <c r="D9" s="2">
         <f>B9+C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2931</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="D10" s="2">
+        <f>B10+C10</f>
         <v/>
       </c>
     </row>
@@ -1164,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1328,6 +1345,23 @@
       </c>
       <c r="D9" s="2">
         <f>B9+C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>11664</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7090</v>
+      </c>
+      <c r="D10" s="2">
+        <f>B10+C10</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1510,6 +1544,23 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D10" s="2">
+        <f>B10+C10</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$10</f>
+              <f>'OssDsign'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$10</f>
+              <f>'OssDsign'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$10</f>
+              <f>'OssDsign'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$10</f>
+              <f>'OssDsign'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$10</f>
+              <f>'Smart Eye'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$10</f>
+              <f>'Smart Eye'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$10</f>
+              <f>'Smart Eye'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$10</f>
+              <f>'Smart Eye'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$10</f>
+              <f>'Integrum'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$10</f>
+              <f>'Integrum'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$10</f>
+              <f>'Integrum'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$10</f>
+              <f>'Integrum'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1166,6 +1166,23 @@
       </c>
       <c r="D10" s="2">
         <f>B10+C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2923</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D11" s="2">
+        <f>B11+C11</f>
         <v/>
       </c>
     </row>
@@ -1181,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1362,6 +1379,23 @@
       </c>
       <c r="D10" s="2">
         <f>B10+C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>11661</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>7101</v>
+      </c>
+      <c r="D11" s="2">
+        <f>B11+C11</f>
         <v/>
       </c>
     </row>
@@ -1377,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1561,6 +1595,23 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2470</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D11" s="2">
+        <f>B11+C11</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$11</f>
+              <f>'OssDsign'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$11</f>
+              <f>'OssDsign'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$11</f>
+              <f>'OssDsign'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$11</f>
+              <f>'OssDsign'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$11</f>
+              <f>'Smart Eye'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$11</f>
+              <f>'Smart Eye'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$11</f>
+              <f>'Smart Eye'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$11</f>
+              <f>'Smart Eye'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$11</f>
+              <f>'Integrum'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$11</f>
+              <f>'Integrum'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$11</f>
+              <f>'Integrum'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$11</f>
+              <f>'Integrum'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1183,23 @@
       </c>
       <c r="D11" s="2">
         <f>B11+C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2923</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D12" s="2">
+        <f>B12+C12</f>
         <v/>
       </c>
     </row>
@@ -1198,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1396,6 +1413,23 @@
       </c>
       <c r="D11" s="2">
         <f>B11+C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11661</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>7101</v>
+      </c>
+      <c r="D12" s="2">
+        <f>B12+C12</f>
         <v/>
       </c>
     </row>
@@ -1411,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1612,6 +1646,23 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D12" s="2">
+        <f>B12+C12</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$12</f>
+              <f>'OssDsign'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$12</f>
+              <f>'OssDsign'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$12</f>
+              <f>'OssDsign'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$12</f>
+              <f>'OssDsign'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$12</f>
+              <f>'Smart Eye'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$12</f>
+              <f>'Smart Eye'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$12</f>
+              <f>'Smart Eye'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$12</f>
+              <f>'Smart Eye'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$12</f>
+              <f>'Integrum'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$12</f>
+              <f>'Integrum'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$12</f>
+              <f>'Integrum'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$12</f>
+              <f>'Integrum'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1200,6 +1200,23 @@
       </c>
       <c r="D12" s="2">
         <f>B12+C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2923</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D13" s="2">
+        <f>B13+C13</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1430,6 +1447,23 @@
       </c>
       <c r="D12" s="2">
         <f>B12+C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>11661</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>7101</v>
+      </c>
+      <c r="D13" s="2">
+        <f>B13+C13</f>
         <v/>
       </c>
     </row>
@@ -1445,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1663,6 +1697,23 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D13" s="2">
+        <f>B13+C13</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$13</f>
+              <f>'OssDsign'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$13</f>
+              <f>'OssDsign'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$13</f>
+              <f>'OssDsign'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$13</f>
+              <f>'OssDsign'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$13</f>
+              <f>'Smart Eye'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$13</f>
+              <f>'Smart Eye'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$13</f>
+              <f>'Smart Eye'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$13</f>
+              <f>'Smart Eye'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$13</f>
+              <f>'Integrum'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$13</f>
+              <f>'Integrum'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$13</f>
+              <f>'Integrum'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$13</f>
+              <f>'Integrum'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1217,6 +1217,23 @@
       </c>
       <c r="D13" s="2">
         <f>B13+C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2923</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="D14" s="2">
+        <f>B14+C14</f>
         <v/>
       </c>
     </row>
@@ -1232,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1464,6 +1481,23 @@
       </c>
       <c r="D13" s="2">
         <f>B13+C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>11661</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>7121</v>
+      </c>
+      <c r="D14" s="2">
+        <f>B14+C14</f>
         <v/>
       </c>
     </row>
@@ -1479,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1714,6 +1748,23 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D14" s="2">
+        <f>B14+C14</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$14</f>
+              <f>'OssDsign'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$14</f>
+              <f>'OssDsign'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$14</f>
+              <f>'OssDsign'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$14</f>
+              <f>'OssDsign'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$14</f>
+              <f>'Smart Eye'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$14</f>
+              <f>'Smart Eye'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$14</f>
+              <f>'Smart Eye'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$14</f>
+              <f>'Smart Eye'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$14</f>
+              <f>'Integrum'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$14</f>
+              <f>'Integrum'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$14</f>
+              <f>'Integrum'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$14</f>
+              <f>'Integrum'!$C$2:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1234,6 +1234,23 @@
       </c>
       <c r="D14" s="2">
         <f>B14+C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2925</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D15" s="2">
+        <f>B15+C15</f>
         <v/>
       </c>
     </row>
@@ -1249,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1498,6 +1515,23 @@
       </c>
       <c r="D14" s="2">
         <f>B14+C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>11673</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>7131</v>
+      </c>
+      <c r="D15" s="2">
+        <f>B15+C15</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1765,6 +1799,23 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2463</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="D15" s="2">
+        <f>B15+C15</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$15</f>
+              <f>'OssDsign'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$15</f>
+              <f>'OssDsign'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$15</f>
+              <f>'OssDsign'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$15</f>
+              <f>'OssDsign'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$15</f>
+              <f>'Smart Eye'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$15</f>
+              <f>'Smart Eye'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$15</f>
+              <f>'Smart Eye'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$15</f>
+              <f>'Smart Eye'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$15</f>
+              <f>'Integrum'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$15</f>
+              <f>'Integrum'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$15</f>
+              <f>'Integrum'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$15</f>
+              <f>'Integrum'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1251,23 @@
       </c>
       <c r="D15" s="2">
         <f>B15+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2888</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="D16" s="2">
+        <f>B16+C16</f>
         <v/>
       </c>
     </row>
@@ -1266,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1532,6 +1549,23 @@
       </c>
       <c r="D15" s="2">
         <f>B15+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>11683</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>7133</v>
+      </c>
+      <c r="D16" s="2">
+        <f>B16+C16</f>
         <v/>
       </c>
     </row>
@@ -1547,7 +1581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1816,6 +1850,23 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2461</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="D16" s="2">
+        <f>B16+C16</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$16</f>
+              <f>'OssDsign'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$16</f>
+              <f>'OssDsign'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$16</f>
+              <f>'OssDsign'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$16</f>
+              <f>'OssDsign'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$16</f>
+              <f>'Smart Eye'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$16</f>
+              <f>'Smart Eye'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$16</f>
+              <f>'Smart Eye'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$16</f>
+              <f>'Smart Eye'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$16</f>
+              <f>'Integrum'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$16</f>
+              <f>'Integrum'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$16</f>
+              <f>'Integrum'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$16</f>
+              <f>'Integrum'!$C$2:$C$17</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,23 @@
       </c>
       <c r="D16" s="2">
         <f>B16+C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2871</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="D17" s="2">
+        <f>B17+C17</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1566,6 +1583,23 @@
       </c>
       <c r="D16" s="2">
         <f>B16+C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>11699</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>7135</v>
+      </c>
+      <c r="D17" s="2">
+        <f>B17+C17</f>
         <v/>
       </c>
     </row>
@@ -1581,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1867,6 +1901,23 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>566</v>
+      </c>
+      <c r="D17" s="2">
+        <f>B17+C17</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$17</f>
+              <f>'OssDsign'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$17</f>
+              <f>'OssDsign'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$17</f>
+              <f>'OssDsign'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$17</f>
+              <f>'OssDsign'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$17</f>
+              <f>'Smart Eye'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$17</f>
+              <f>'Smart Eye'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$17</f>
+              <f>'Smart Eye'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$17</f>
+              <f>'Smart Eye'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$17</f>
+              <f>'Integrum'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$17</f>
+              <f>'Integrum'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$17</f>
+              <f>'Integrum'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$17</f>
+              <f>'Integrum'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1285,6 +1285,23 @@
       </c>
       <c r="D17" s="2">
         <f>B17+C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2865</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="D18" s="2">
+        <f>B18+C18</f>
         <v/>
       </c>
     </row>
@@ -1300,7 +1317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1600,6 +1617,23 @@
       </c>
       <c r="D17" s="2">
         <f>B17+C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11708</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7140</v>
+      </c>
+      <c r="D18" s="2">
+        <f>B18+C18</f>
         <v/>
       </c>
     </row>
@@ -1615,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1918,6 +1952,23 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D18" s="2">
+        <f>B18+C18</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$18</f>
+              <f>'OssDsign'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$18</f>
+              <f>'OssDsign'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$18</f>
+              <f>'OssDsign'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$18</f>
+              <f>'OssDsign'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$18</f>
+              <f>'Smart Eye'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$18</f>
+              <f>'Smart Eye'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$18</f>
+              <f>'Smart Eye'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$18</f>
+              <f>'Smart Eye'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$18</f>
+              <f>'Integrum'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$18</f>
+              <f>'Integrum'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$18</f>
+              <f>'Integrum'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$18</f>
+              <f>'Integrum'!$C$2:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1302,6 +1302,23 @@
       </c>
       <c r="D18" s="2">
         <f>B18+C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2862</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="D19" s="2">
+        <f>B19+C19</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1634,6 +1651,23 @@
       </c>
       <c r="D18" s="2">
         <f>B18+C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>11702</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="D19" s="2">
+        <f>B19+C19</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1969,6 +2003,23 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D19" s="2">
+        <f>B19+C19</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$19</f>
+              <f>'OssDsign'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$19</f>
+              <f>'OssDsign'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$19</f>
+              <f>'OssDsign'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$19</f>
+              <f>'OssDsign'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$19</f>
+              <f>'Smart Eye'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$19</f>
+              <f>'Smart Eye'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$19</f>
+              <f>'Smart Eye'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$19</f>
+              <f>'Smart Eye'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$19</f>
+              <f>'Integrum'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$19</f>
+              <f>'Integrum'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$19</f>
+              <f>'Integrum'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$19</f>
+              <f>'Integrum'!$C$2:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1319,6 +1319,23 @@
       </c>
       <c r="D19" s="2">
         <f>B19+C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2862</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="D20" s="2">
+        <f>B20+C20</f>
         <v/>
       </c>
     </row>
@@ -1334,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1668,6 +1685,23 @@
       </c>
       <c r="D19" s="2">
         <f>B19+C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>11702</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="D20" s="2">
+        <f>B20+C20</f>
         <v/>
       </c>
     </row>
@@ -1683,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2054,23 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D20" s="2">
+        <f>B20+C20</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$20</f>
+              <f>'OssDsign'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$20</f>
+              <f>'OssDsign'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$20</f>
+              <f>'OssDsign'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$20</f>
+              <f>'OssDsign'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$20</f>
+              <f>'Smart Eye'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$20</f>
+              <f>'Smart Eye'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$20</f>
+              <f>'Smart Eye'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$20</f>
+              <f>'Smart Eye'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$20</f>
+              <f>'Integrum'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$20</f>
+              <f>'Integrum'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$20</f>
+              <f>'Integrum'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$20</f>
+              <f>'Integrum'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1336,6 +1336,23 @@
       </c>
       <c r="D20" s="2">
         <f>B20+C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2862</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="D21" s="2">
+        <f>B21+C21</f>
         <v/>
       </c>
     </row>
@@ -1351,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1702,6 +1719,23 @@
       </c>
       <c r="D20" s="2">
         <f>B20+C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>11702</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>7149</v>
+      </c>
+      <c r="D21" s="2">
+        <f>B21+C21</f>
         <v/>
       </c>
     </row>
@@ -1717,7 +1751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2105,23 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D21" s="2">
+        <f>B21+C21</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$21</f>
+              <f>'OssDsign'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$21</f>
+              <f>'OssDsign'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$21</f>
+              <f>'OssDsign'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$21</f>
+              <f>'OssDsign'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$21</f>
+              <f>'Smart Eye'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$21</f>
+              <f>'Smart Eye'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$21</f>
+              <f>'Smart Eye'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$21</f>
+              <f>'Smart Eye'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$21</f>
+              <f>'Integrum'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$21</f>
+              <f>'Integrum'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$21</f>
+              <f>'Integrum'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$21</f>
+              <f>'Integrum'!$C$2:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1353,6 +1353,23 @@
       </c>
       <c r="D21" s="2">
         <f>B21+C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2861</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="D22" s="2">
+        <f>B22+C22</f>
         <v/>
       </c>
     </row>
@@ -1368,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1736,6 +1753,23 @@
       </c>
       <c r="D21" s="2">
         <f>B21+C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>11872</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>7171</v>
+      </c>
+      <c r="D22" s="2">
+        <f>B22+C22</f>
         <v/>
       </c>
     </row>
@@ -1751,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2122,6 +2156,23 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2457</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="D22" s="2">
+        <f>B22+C22</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$22</f>
+              <f>'OssDsign'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$22</f>
+              <f>'OssDsign'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$22</f>
+              <f>'OssDsign'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$22</f>
+              <f>'OssDsign'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$22</f>
+              <f>'Smart Eye'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$22</f>
+              <f>'Smart Eye'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$22</f>
+              <f>'Smart Eye'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$22</f>
+              <f>'Smart Eye'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$22</f>
+              <f>'Integrum'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$22</f>
+              <f>'Integrum'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$22</f>
+              <f>'Integrum'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$22</f>
+              <f>'Integrum'!$C$2:$C$23</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1370,6 +1370,23 @@
       </c>
       <c r="D22" s="2">
         <f>B22+C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2861</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="D23" s="2">
+        <f>B23+C23</f>
         <v/>
       </c>
     </row>
@@ -1385,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1770,6 +1787,23 @@
       </c>
       <c r="D22" s="2">
         <f>B22+C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>12277</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>7212</v>
+      </c>
+      <c r="D23" s="2">
+        <f>B23+C23</f>
         <v/>
       </c>
     </row>
@@ -1785,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2207,23 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="D23" s="2">
+        <f>B23+C23</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$23</f>
+              <f>'OssDsign'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$23</f>
+              <f>'OssDsign'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$23</f>
+              <f>'OssDsign'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$23</f>
+              <f>'OssDsign'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$23</f>
+              <f>'Smart Eye'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$23</f>
+              <f>'Smart Eye'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$23</f>
+              <f>'Smart Eye'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$23</f>
+              <f>'Smart Eye'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$23</f>
+              <f>'Integrum'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$23</f>
+              <f>'Integrum'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$23</f>
+              <f>'Integrum'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$23</f>
+              <f>'Integrum'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1387,23 @@
       </c>
       <c r="D23" s="2">
         <f>B23+C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2863</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="D24" s="2">
+        <f>B24+C24</f>
         <v/>
       </c>
     </row>
@@ -1402,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1804,6 +1821,23 @@
       </c>
       <c r="D23" s="2">
         <f>B23+C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>13412</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>7535</v>
+      </c>
+      <c r="D24" s="2">
+        <f>B24+C24</f>
         <v/>
       </c>
     </row>
@@ -1819,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2258,23 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2461</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D24" s="2">
+        <f>B24+C24</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$24</f>
+              <f>'OssDsign'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$24</f>
+              <f>'OssDsign'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$24</f>
+              <f>'OssDsign'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$24</f>
+              <f>'OssDsign'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$24</f>
+              <f>'Smart Eye'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$24</f>
+              <f>'Smart Eye'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$24</f>
+              <f>'Smart Eye'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$24</f>
+              <f>'Smart Eye'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$24</f>
+              <f>'Integrum'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$24</f>
+              <f>'Integrum'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$24</f>
+              <f>'Integrum'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$24</f>
+              <f>'Integrum'!$C$2:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1404,6 +1404,23 @@
       </c>
       <c r="D24" s="2">
         <f>B24+C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2862</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="D25" s="2">
+        <f>B25+C25</f>
         <v/>
       </c>
     </row>
@@ -1419,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1838,6 +1855,23 @@
       </c>
       <c r="D24" s="2">
         <f>B24+C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>13715</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>7443</v>
+      </c>
+      <c r="D25" s="2">
+        <f>B25+C25</f>
         <v/>
       </c>
     </row>
@@ -1853,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2275,6 +2309,23 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2461</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D25" s="2">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$25</f>
+              <f>'OssDsign'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$25</f>
+              <f>'OssDsign'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$25</f>
+              <f>'OssDsign'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$25</f>
+              <f>'OssDsign'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$25</f>
+              <f>'Smart Eye'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$25</f>
+              <f>'Smart Eye'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$25</f>
+              <f>'Smart Eye'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$25</f>
+              <f>'Smart Eye'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$25</f>
+              <f>'Integrum'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$25</f>
+              <f>'Integrum'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$25</f>
+              <f>'Integrum'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$25</f>
+              <f>'Integrum'!$C$2:$C$26</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1421,6 +1421,23 @@
       </c>
       <c r="D25" s="2">
         <f>B25+C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2862</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="D26" s="2">
+        <f>B26+C26</f>
         <v/>
       </c>
     </row>
@@ -1436,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1872,6 +1889,23 @@
       </c>
       <c r="D25" s="2">
         <f>B25+C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>13715</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>7443</v>
+      </c>
+      <c r="D26" s="2">
+        <f>B26+C26</f>
         <v/>
       </c>
     </row>
@@ -1887,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2326,6 +2360,23 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2461</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D26" s="2">
+        <f>B26+C26</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$26</f>
+              <f>'OssDsign'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$26</f>
+              <f>'OssDsign'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$26</f>
+              <f>'OssDsign'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$26</f>
+              <f>'OssDsign'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$26</f>
+              <f>'Smart Eye'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$26</f>
+              <f>'Smart Eye'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$26</f>
+              <f>'Smart Eye'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$26</f>
+              <f>'Smart Eye'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$26</f>
+              <f>'Integrum'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$26</f>
+              <f>'Integrum'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$26</f>
+              <f>'Integrum'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$26</f>
+              <f>'Integrum'!$C$2:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1438,6 +1438,23 @@
       </c>
       <c r="D26" s="2">
         <f>B26+C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>694</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27+C27</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1923,23 @@
       </c>
       <c r="D26" s="2">
         <f>B26+C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>13860</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>7443</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27+C27</f>
         <v/>
       </c>
     </row>
@@ -1921,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2411,23 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27+C27</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$27</f>
+              <f>'OssDsign'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$27</f>
+              <f>'OssDsign'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$27</f>
+              <f>'OssDsign'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$27</f>
+              <f>'OssDsign'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$27</f>
+              <f>'Smart Eye'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$27</f>
+              <f>'Smart Eye'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$27</f>
+              <f>'Smart Eye'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$27</f>
+              <f>'Smart Eye'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$27</f>
+              <f>'Integrum'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$27</f>
+              <f>'Integrum'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$27</f>
+              <f>'Integrum'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$27</f>
+              <f>'Integrum'!$C$2:$C$28</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1455,6 +1455,23 @@
       </c>
       <c r="D27" s="2">
         <f>B27+C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>687</v>
+      </c>
+      <c r="D28" s="2">
+        <f>B28+C28</f>
         <v/>
       </c>
     </row>
@@ -1470,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1940,6 +1957,23 @@
       </c>
       <c r="D27" s="2">
         <f>B27+C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>13860</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>7498</v>
+      </c>
+      <c r="D28" s="2">
+        <f>B28+C28</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2462,23 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="D28" s="2">
+        <f>B28+C28</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$28</f>
+              <f>'OssDsign'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$28</f>
+              <f>'OssDsign'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$28</f>
+              <f>'OssDsign'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$28</f>
+              <f>'OssDsign'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$28</f>
+              <f>'Smart Eye'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$28</f>
+              <f>'Smart Eye'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$28</f>
+              <f>'Smart Eye'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$28</f>
+              <f>'Smart Eye'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$28</f>
+              <f>'Integrum'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$28</f>
+              <f>'Integrum'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$28</f>
+              <f>'Integrum'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$28</f>
+              <f>'Integrum'!$C$2:$C$29</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1472,6 +1472,23 @@
       </c>
       <c r="D28" s="2">
         <f>B28+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2856</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>686</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29+C29</f>
         <v/>
       </c>
     </row>
@@ -1487,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1974,6 +1991,23 @@
       </c>
       <c r="D28" s="2">
         <f>B28+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>14074</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>7549</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29+C29</f>
         <v/>
       </c>
     </row>
@@ -1989,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2479,6 +2513,23 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2458</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D29" s="2">
+        <f>B29+C29</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$29</f>
+              <f>'OssDsign'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$29</f>
+              <f>'OssDsign'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$29</f>
+              <f>'OssDsign'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$29</f>
+              <f>'OssDsign'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$29</f>
+              <f>'Smart Eye'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$29</f>
+              <f>'Smart Eye'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$29</f>
+              <f>'Smart Eye'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$29</f>
+              <f>'Smart Eye'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$29</f>
+              <f>'Integrum'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$29</f>
+              <f>'Integrum'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$29</f>
+              <f>'Integrum'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$29</f>
+              <f>'Integrum'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1489,6 +1489,23 @@
       </c>
       <c r="D29" s="2">
         <f>B29+C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2852</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="D30" s="2">
+        <f>B30+C30</f>
         <v/>
       </c>
     </row>
@@ -1504,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2008,6 +2025,23 @@
       </c>
       <c r="D29" s="2">
         <f>B29+C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>14040</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>7561</v>
+      </c>
+      <c r="D30" s="2">
+        <f>B30+C30</f>
         <v/>
       </c>
     </row>
@@ -2023,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2530,6 +2564,23 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2465</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D30" s="2">
+        <f>B30+C30</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$30</f>
+              <f>'OssDsign'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$30</f>
+              <f>'OssDsign'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$30</f>
+              <f>'OssDsign'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$30</f>
+              <f>'OssDsign'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$30</f>
+              <f>'Smart Eye'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$30</f>
+              <f>'Smart Eye'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$30</f>
+              <f>'Smart Eye'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$30</f>
+              <f>'Smart Eye'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$30</f>
+              <f>'Integrum'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$30</f>
+              <f>'Integrum'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$30</f>
+              <f>'Integrum'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$30</f>
+              <f>'Integrum'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,23 @@
       </c>
       <c r="D30" s="2">
         <f>B30+C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2848</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D31" s="2">
+        <f>B31+C31</f>
         <v/>
       </c>
     </row>
@@ -1521,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2059,23 @@
       </c>
       <c r="D30" s="2">
         <f>B30+C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>14047</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7577</v>
+      </c>
+      <c r="D31" s="2">
+        <f>B31+C31</f>
         <v/>
       </c>
     </row>
@@ -2057,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2581,6 +2615,23 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2469</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="D31" s="2">
+        <f>B31+C31</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$31</f>
+              <f>'OssDsign'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$31</f>
+              <f>'OssDsign'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$31</f>
+              <f>'OssDsign'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$31</f>
+              <f>'OssDsign'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$31</f>
+              <f>'Smart Eye'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$31</f>
+              <f>'Smart Eye'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$31</f>
+              <f>'Smart Eye'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$31</f>
+              <f>'Smart Eye'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$31</f>
+              <f>'Integrum'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$31</f>
+              <f>'Integrum'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$31</f>
+              <f>'Integrum'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$31</f>
+              <f>'Integrum'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1523,6 +1523,23 @@
       </c>
       <c r="D31" s="2">
         <f>B31+C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2841</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D32" s="2">
+        <f>B32+C32</f>
         <v/>
       </c>
     </row>
@@ -1538,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2093,23 @@
       </c>
       <c r="D31" s="2">
         <f>B31+C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>14047</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>7502</v>
+      </c>
+      <c r="D32" s="2">
+        <f>B32+C32</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2632,6 +2666,23 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2486</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="D32" s="2">
+        <f>B32+C32</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$32</f>
+              <f>'OssDsign'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$32</f>
+              <f>'OssDsign'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$32</f>
+              <f>'OssDsign'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$32</f>
+              <f>'OssDsign'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$32</f>
+              <f>'Smart Eye'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$32</f>
+              <f>'Smart Eye'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$32</f>
+              <f>'Smart Eye'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$32</f>
+              <f>'Smart Eye'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$32</f>
+              <f>'Integrum'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$32</f>
+              <f>'Integrum'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$32</f>
+              <f>'Integrum'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$32</f>
+              <f>'Integrum'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1540,6 +1540,23 @@
       </c>
       <c r="D32" s="2">
         <f>B32+C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2840</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D33" s="2">
+        <f>B33+C33</f>
         <v/>
       </c>
     </row>
@@ -1555,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2127,23 @@
       </c>
       <c r="D32" s="2">
         <f>B32+C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>14032</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>7502</v>
+      </c>
+      <c r="D33" s="2">
+        <f>B33+C33</f>
         <v/>
       </c>
     </row>
@@ -2125,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2683,6 +2717,23 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="D33" s="2">
+        <f>B33+C33</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$33</f>
+              <f>'OssDsign'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$33</f>
+              <f>'OssDsign'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$33</f>
+              <f>'OssDsign'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$33</f>
+              <f>'OssDsign'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$33</f>
+              <f>'Smart Eye'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$33</f>
+              <f>'Smart Eye'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$33</f>
+              <f>'Smart Eye'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$33</f>
+              <f>'Smart Eye'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$33</f>
+              <f>'Integrum'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$33</f>
+              <f>'Integrum'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$33</f>
+              <f>'Integrum'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$33</f>
+              <f>'Integrum'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1557,6 +1557,23 @@
       </c>
       <c r="D33" s="2">
         <f>B33+C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2840</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D34" s="2">
+        <f>B34+C34</f>
         <v/>
       </c>
     </row>
@@ -1572,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2144,6 +2161,23 @@
       </c>
       <c r="D33" s="2">
         <f>B33+C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>14032</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>7502</v>
+      </c>
+      <c r="D34" s="2">
+        <f>B34+C34</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2734,6 +2768,23 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="D34" s="2">
+        <f>B34+C34</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$34</f>
+              <f>'OssDsign'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$34</f>
+              <f>'OssDsign'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$34</f>
+              <f>'OssDsign'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$34</f>
+              <f>'OssDsign'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$34</f>
+              <f>'Smart Eye'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$34</f>
+              <f>'Smart Eye'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$34</f>
+              <f>'Smart Eye'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$34</f>
+              <f>'Smart Eye'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$34</f>
+              <f>'Integrum'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$34</f>
+              <f>'Integrum'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$34</f>
+              <f>'Integrum'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$34</f>
+              <f>'Integrum'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1574,6 +1574,23 @@
       </c>
       <c r="D34" s="2">
         <f>B34+C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2840</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>682</v>
+      </c>
+      <c r="D35" s="2">
+        <f>B35+C35</f>
         <v/>
       </c>
     </row>
@@ -1589,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2195,23 @@
       </c>
       <c r="D34" s="2">
         <f>B34+C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>14032</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>7420</v>
+      </c>
+      <c r="D35" s="2">
+        <f>B35+C35</f>
         <v/>
       </c>
     </row>
@@ -2193,7 +2227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2785,6 +2819,23 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D35" s="2">
+        <f>B35+C35</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$35</f>
+              <f>'OssDsign'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$35</f>
+              <f>'OssDsign'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$35</f>
+              <f>'OssDsign'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$35</f>
+              <f>'OssDsign'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$35</f>
+              <f>'Smart Eye'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$35</f>
+              <f>'Smart Eye'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$35</f>
+              <f>'Smart Eye'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$35</f>
+              <f>'Smart Eye'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$35</f>
+              <f>'Integrum'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$35</f>
+              <f>'Integrum'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$35</f>
+              <f>'Integrum'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$35</f>
+              <f>'Integrum'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1591,6 +1591,23 @@
       </c>
       <c r="D35" s="2">
         <f>B35+C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2836</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>681</v>
+      </c>
+      <c r="D36" s="2">
+        <f>B36+C36</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2229,23 @@
       </c>
       <c r="D35" s="2">
         <f>B35+C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>13968</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>7399</v>
+      </c>
+      <c r="D36" s="2">
+        <f>B36+C36</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2836,6 +2870,23 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="D36" s="2">
+        <f>B36+C36</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$36</f>
+              <f>'OssDsign'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$36</f>
+              <f>'OssDsign'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$36</f>
+              <f>'OssDsign'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$36</f>
+              <f>'OssDsign'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$36</f>
+              <f>'Smart Eye'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$36</f>
+              <f>'Smart Eye'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$36</f>
+              <f>'Smart Eye'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$36</f>
+              <f>'Smart Eye'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$36</f>
+              <f>'Integrum'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$36</f>
+              <f>'Integrum'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$36</f>
+              <f>'Integrum'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$36</f>
+              <f>'Integrum'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1608,23 @@
       </c>
       <c r="D36" s="2">
         <f>B36+C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2832</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="D37" s="2">
+        <f>B37+C37</f>
         <v/>
       </c>
     </row>
@@ -1623,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2263,23 @@
       </c>
       <c r="D36" s="2">
         <f>B36+C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>13886</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>7345</v>
+      </c>
+      <c r="D37" s="2">
+        <f>B37+C37</f>
         <v/>
       </c>
     </row>
@@ -2261,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2887,6 +2921,23 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D37" s="2">
+        <f>B37+C37</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$37</f>
+              <f>'OssDsign'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$37</f>
+              <f>'OssDsign'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$37</f>
+              <f>'OssDsign'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$37</f>
+              <f>'OssDsign'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$37</f>
+              <f>'Smart Eye'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$37</f>
+              <f>'Smart Eye'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$37</f>
+              <f>'Smart Eye'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$37</f>
+              <f>'Smart Eye'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$37</f>
+              <f>'Integrum'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$37</f>
+              <f>'Integrum'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$37</f>
+              <f>'Integrum'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$37</f>
+              <f>'Integrum'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1625,6 +1625,23 @@
       </c>
       <c r="D37" s="2">
         <f>B37+C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2829</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>677</v>
+      </c>
+      <c r="D38" s="2">
+        <f>B38+C38</f>
         <v/>
       </c>
     </row>
@@ -1640,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2280,6 +2297,23 @@
       </c>
       <c r="D37" s="2">
         <f>B37+C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>13840</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>7291</v>
+      </c>
+      <c r="D38" s="2">
+        <f>B38+C38</f>
         <v/>
       </c>
     </row>
@@ -2295,7 +2329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2938,6 +2972,23 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2484</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D38" s="2">
+        <f>B38+C38</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$38</f>
+              <f>'OssDsign'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$38</f>
+              <f>'OssDsign'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$38</f>
+              <f>'OssDsign'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$38</f>
+              <f>'OssDsign'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$38</f>
+              <f>'Smart Eye'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$38</f>
+              <f>'Smart Eye'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$38</f>
+              <f>'Smart Eye'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$38</f>
+              <f>'Smart Eye'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$38</f>
+              <f>'Integrum'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$38</f>
+              <f>'Integrum'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$38</f>
+              <f>'Integrum'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$38</f>
+              <f>'Integrum'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1642,6 +1642,23 @@
       </c>
       <c r="D38" s="2">
         <f>B38+C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2824</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="D39" s="2">
+        <f>B39+C39</f>
         <v/>
       </c>
     </row>
@@ -1657,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2314,6 +2331,23 @@
       </c>
       <c r="D38" s="2">
         <f>B38+C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>13825</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>7263</v>
+      </c>
+      <c r="D39" s="2">
+        <f>B39+C39</f>
         <v/>
       </c>
     </row>
@@ -2329,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2989,6 +3023,23 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2481</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D39" s="2">
+        <f>B39+C39</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$39</f>
+              <f>'OssDsign'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$39</f>
+              <f>'OssDsign'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$39</f>
+              <f>'OssDsign'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$39</f>
+              <f>'OssDsign'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$39</f>
+              <f>'Smart Eye'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$39</f>
+              <f>'Smart Eye'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$39</f>
+              <f>'Smart Eye'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$39</f>
+              <f>'Smart Eye'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$39</f>
+              <f>'Integrum'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$39</f>
+              <f>'Integrum'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$39</f>
+              <f>'Integrum'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$39</f>
+              <f>'Integrum'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1659,6 +1659,23 @@
       </c>
       <c r="D39" s="2">
         <f>B39+C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2822</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="D40" s="2">
+        <f>B40+C40</f>
         <v/>
       </c>
     </row>
@@ -1674,7 +1691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2348,6 +2365,23 @@
       </c>
       <c r="D39" s="2">
         <f>B39+C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>13828</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>7263</v>
+      </c>
+      <c r="D40" s="2">
+        <f>B40+C40</f>
         <v/>
       </c>
     </row>
@@ -2363,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3040,6 +3074,23 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2477</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D40" s="2">
+        <f>B40+C40</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
